--- a/Data/Home/LivingRoom.Window001.xlsx
+++ b/Data/Home/LivingRoom.Window001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709439284</v>
+        <v>1713160236</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709459154</v>
+        <v>1713169972</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709608949</v>
+        <v>1713244451</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709625844</v>
+        <v>1713260704</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709716406</v>
+        <v>1713332699</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709859839</v>
+        <v>1713349290</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709866135</v>
+        <v>1713512469</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709876860</v>
+        <v>1713523046</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1710820505</v>
+        <v>1713624211</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1710832577</v>
+        <v>1713774263</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1711082474</v>
+        <v>1713850177</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1711095965</v>
+        <v>1713868193</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1711635029</v>
+        <v>1713934798</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,44 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1713946078</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LivingRoom.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
